--- a/Altium/Snap4/PCBWay/Snap4.xlsx
+++ b/Altium/Snap4/PCBWay/Snap4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\w\snap\Altium\Snap4\Project Outputs for Snap4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\w\snap\Altium\Snap4\PCBWay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B80127-0CCF-4AD9-8D55-E4736871EFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FA902A-DD51-4638-A11A-03D5E7D591F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="21180" windowHeight="15585" xr2:uid="{5DDAE8C7-BE36-4E37-BAF0-231222486A98}"/>
+    <workbookView xWindow="47970" yWindow="765" windowWidth="19500" windowHeight="14640" xr2:uid="{5DDAE8C7-BE36-4E37-BAF0-231222486A98}"/>
   </bookViews>
   <sheets>
     <sheet name="Snap4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="146">
   <si>
     <t>Comment</t>
   </si>
@@ -62,9 +62,6 @@
     <t>XTAL_ABS06</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>*1</t>
   </si>
   <si>
@@ -371,9 +368,6 @@
     <t>WM4925-ND</t>
   </si>
   <si>
-    <t>Header 3 pin</t>
-  </si>
-  <si>
     <t>LP3985IM5-3.3/NOPBTR-ND</t>
   </si>
   <si>
@@ -471,13 +465,25 @@
   </si>
   <si>
     <t>ideal diode</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>CONN HEADER R/A 2POS 2.54MM</t>
+  </si>
+  <si>
+    <t>WM4924-ND</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,15 +504,25 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF444444"/>
-      <name val="Roboto"/>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -524,12 +540,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -556,15 +572,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -576,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -585,21 +592,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,11 +942,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3316A50C-7F24-437D-AF6B-7E0C7410C498}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="3" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="46.5703125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
     <col min="4" max="4" width="32.85546875" customWidth="1"/>
     <col min="5" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -948,11 +957,11 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -965,23 +974,26 @@
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>114</v>
+      <c r="B2" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
@@ -992,20 +1004,20 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>93</v>
+        <v>9</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="G3" s="1">
         <v>7</v>
@@ -1013,20 +1025,20 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>94</v>
+        <v>12</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -1034,20 +1046,20 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>93</v>
+        <v>15</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -1055,22 +1067,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="G6" s="1">
         <v>8</v>
@@ -1078,20 +1090,20 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>95</v>
+        <v>19</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -1099,22 +1111,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1122,22 +1134,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1145,22 +1157,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1168,22 +1180,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1191,22 +1203,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1214,22 +1226,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -1237,22 +1249,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1260,69 +1272,66 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>119</v>
+        <v>42</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>705530036</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>705530037</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -1330,22 +1339,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -1353,22 +1362,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -1376,22 +1385,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -1399,202 +1408,202 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G21" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>122</v>
+        <v>58</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>123</v>
+        <v>60</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>142</v>
+        <v>62</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>143</v>
+        <v>122</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>65</v>
+      <c r="H25" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>126</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G26" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>111</v>
+        <v>69</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>112</v>
+        <v>71</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>127</v>
+        <v>75</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -1602,70 +1611,93 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>129</v>
+        <v>78</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>113</v>
+        <v>82</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C33" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G32" s="1">
+      <c r="F33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="1">
         <v>1</v>
       </c>
     </row>
